--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D3">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="H3">
         <v>426</v>
